--- a/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Ordenes_de_Renta_Fija.xlsx
+++ b/Plantillas_carga_masiva/Panama/Estructura_Cargue_Masivo_Ordenes_de_Renta_Fija.xlsx
@@ -146,7 +146,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A1000">
-      <formula1>Listas!$A$2:$A$20</formula1>
+      <formula1>Listas!$A$2:$A$15</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B1000">
       <formula1>Listas!$B$2:$B$3</formula1>
@@ -508,7 +508,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julian Andres Mesa Restrepo</t>
+          <t xml:space="preserve">FONDO INMOBILIARIO 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -525,7 +525,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andres Julian Murillo Lopez</t>
+          <t xml:space="preserve">FONDO ALTERNATIVO 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustavo Saldarriaga</t>
+          <t xml:space="preserve">FVP CONSERVADOR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paula Andrea Alvarez</t>
+          <t xml:space="preserve">FVP MODERADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grupo Corporativo Jham</t>
+          <t xml:space="preserve">FVP AGRESIVO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -587,91 +587,6 @@
       <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">SURA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FONDO INMOBILIARIO 1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FONDO ALTERNATIVO 1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FVP CONSERVADOR</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FVP MODERADO</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FVP AGRESIVO</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
